--- a/Igualdad/cuadro_porcentajes/CUADRO_PORCENTAJES.xlsx
+++ b/Igualdad/cuadro_porcentajes/CUADRO_PORCENTAJES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Igualdad\cuadro_porcentajes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB668735-B1C4-490A-A70D-9D8D855ABABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62280010-6084-403F-9725-97D94C2AD094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{1EBB73AE-3F64-4B2B-9500-41EA18FDCE58}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TOTAL PLANTILLA" sheetId="27" r:id="rId1"/>
@@ -53,6 +53,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="97">
   <si>
     <t>Menos de 20 años</t>
   </si>
@@ -333,12 +334,6 @@
     <t>Porcentaje Jornada</t>
   </si>
   <si>
-    <t>60 años</t>
-  </si>
-  <si>
-    <t>63 años</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -358,6 +353,9 @@
   </si>
   <si>
     <t>Duración determinada jornada parcial</t>
+  </si>
+  <si>
+    <t>más 60 años</t>
   </si>
 </sst>
 </file>
@@ -1689,372 +1687,6 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>FORMACIÓN!$C$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>FORMACIÓN!$D$7:$E$7</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>MUJERES</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>HOMBRES</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>FORMACIÓN!$D$8:$E$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F9D1-494A-90BC-6D8BFBEE3DAB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>FORMACIÓN!$C$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>FORMACIÓN!$D$7:$E$7</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>MUJERES</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>HOMBRES</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>FORMACIÓN!$D$9:$E$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F9D1-494A-90BC-6D8BFBEE3DAB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="644664840"/>
-        <c:axId val="644668080"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="644664840"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="644668080"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="644668080"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="644664840"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
               <c:f>'GRUPO PROFESIONAL'!$D$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -2479,7 +2111,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -2887,7 +2519,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -2943,7 +2575,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'EDAD NNCC'!$D$17</c:f>
+              <c:f>'EDAD NNCC'!$D$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2964,9 +2596,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'EDAD NNCC'!$C$18:$C$29</c:f>
+              <c:f>'EDAD NNCC'!$C$16:$C$25</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>Menos de 20 años</c:v>
                 </c:pt>
@@ -2996,22 +2628,16 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>Más 60 años</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>61 años</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>62 años</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'EDAD NNCC'!$D$18:$D$29</c:f>
+              <c:f>'EDAD NNCC'!$D$16:$D$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3040,12 +2666,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3062,7 +2682,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'EDAD NNCC'!$E$17</c:f>
+              <c:f>'EDAD NNCC'!$E$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3083,9 +2703,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'EDAD NNCC'!$C$18:$C$29</c:f>
+              <c:f>'EDAD NNCC'!$C$16:$C$25</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>Menos de 20 años</c:v>
                 </c:pt>
@@ -3115,22 +2735,16 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>Más 60 años</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>61 años</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>62 años</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'EDAD NNCC'!$E$18:$E$29</c:f>
+              <c:f>'EDAD NNCC'!$E$16:$E$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3159,12 +2773,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3371,7 +2979,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -3779,7 +3387,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -4175,7 +3783,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -4667,7 +4275,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -5075,6 +4683,402 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$E$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MUJERES</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$D$10:$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Parcial               (0% - 38%)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Parcial                     (39% - 75%)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Parcial                    (76% - 99%)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Completa (100%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$E$10:$E$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AB9E-418C-83C5-8D26D80CF5DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$F$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HOMBRES</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$D$10:$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Parcial               (0% - 38%)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Parcial                     (39% - 75%)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Parcial                    (76% - 99%)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Completa (100%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$F$10:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AB9E-418C-83C5-8D26D80CF5DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="644643600"/>
+        <c:axId val="644644320"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="644643600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="644644320"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="644644320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="644643600"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -5160,7 +5164,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>EDAD!$D$19</c:f>
+              <c:f>EDAD!$D$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5181,9 +5185,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>EDAD!$C$20:$C$32</c:f>
+              <c:f>EDAD!$C$17:$C$26</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>Menos de 20 años</c:v>
                 </c:pt>
@@ -5212,26 +5216,17 @@
                   <c:v>55-59 años</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>60 años</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>61 años</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>62 años</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>63 años</c:v>
+                  <c:v>más 60 años</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>EDAD!$D$20:$D$32</c:f>
+              <c:f>EDAD!$D$17:$D$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5276,7 +5271,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>EDAD!$E$19</c:f>
+              <c:f>EDAD!$E$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5297,9 +5292,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>EDAD!$C$20:$C$32</c:f>
+              <c:f>EDAD!$C$17:$C$26</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>Menos de 20 años</c:v>
                 </c:pt>
@@ -5328,26 +5323,17 @@
                   <c:v>55-59 años</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>60 años</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>61 años</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>62 años</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>63 años</c:v>
+                  <c:v>más 60 años</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>EDAD!$E$20:$E$32</c:f>
+              <c:f>EDAD!$E$17:$E$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5670,402 +5656,6 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$E$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>MUJERES</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$D$10:$D$13</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Parcial               (0% - 38%)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Parcial                     (39% - 75%)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Parcial                    (76% - 99%)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Completa (100%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$E$10:$E$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AB9E-418C-83C5-8D26D80CF5DA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$F$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>HOMBRES</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$D$10:$D$13</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Parcial               (0% - 38%)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Parcial                     (39% - 75%)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Parcial                    (76% - 99%)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Completa (100%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'PORCENTAJE JORNADA PERSONAL SUB'!$F$10:$F$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AB9E-418C-83C5-8D26D80CF5DA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="644643600"/>
-        <c:axId val="644644320"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="644643600"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="644644320"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="644644320"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="644643600"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
               <c:f>'PUESTOS DIRECTIVOS PERSONAL SUB'!$D$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -6420,7 +6010,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -10213,46 +9803,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors22.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -13065,7 +12615,7 @@
 </file>
 
 <file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -13269,22 +12819,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -13389,8 +12940,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -13522,19 +13073,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -13568,7 +13120,7 @@
 </file>
 
 <file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -13772,23 +13324,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -13893,8 +13444,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -14026,20 +13577,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -17137,509 +16687,6 @@
 </file>
 
 <file path=xl/charts/style21.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style22.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -21798,47 +20845,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>61912</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF5DE1C5-E0C9-555C-8012-53B234A427C5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>166687</xdr:rowOff>
@@ -21875,7 +20881,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -21916,19 +20922,19 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>166687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>52387</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -21957,7 +20963,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -21998,7 +21004,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -22039,7 +21045,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -22080,7 +21086,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -22121,7 +21127,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -22162,48 +21168,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87BBFE33-7DC1-3A14-03BC-94BA3D83E713}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -22244,7 +21209,48 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87BBFE33-7DC1-3A14-03BC-94BA3D83E713}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -22904,13 +21910,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB83E845-4775-45B8-A384-31FE60335A99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B2" s="22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>12</v>
@@ -22936,7 +21942,7 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="e">
@@ -22981,7 +21987,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -22993,7 +21999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF514AA9-5DFC-46ED-BA5E-921C01C5A133}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B3:N15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23334,7 +22340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD3550A-2C62-4E75-95D5-3295FF3F267E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B2:N14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23675,7 +22681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59150873-790E-48CB-A7B8-C831330DCA38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B2:N37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24464,7 +23470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E92E48C-9FAC-4D60-A1E6-FEFF8F844A87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="B2:N11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24745,7 +23751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8291975D-1AC0-49D6-968C-6A61DC60ACD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="B2:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24966,8 +23972,8 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8139C932-8095-46B3-B9B1-E02C5A5E058E}">
-  <dimension ref="B2:N9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="B2:N7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -25022,11 +24028,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E3" s="2" t="e">
-        <f>C3/$C$5*100</f>
+        <f>C3/$C$4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F3" s="2" t="e">
-        <f>C3/$L$5*100</f>
+        <f>C3/$L$4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="2"/>
@@ -25035,11 +24041,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I3" s="2" t="e">
-        <f>G3/$G$5*100</f>
+        <f>G3/$G$4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J3" s="2" t="e">
-        <f>G3/$L$5*100</f>
+        <f>G3/$L$4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K3" s="2" t="e">
@@ -25060,126 +24066,69 @@
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="5"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="e">
-        <f>C4/L4*100</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C4" s="2">
+        <f>SUM(C3:C3)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2" t="e">
-        <f>C4/$C$5*100</f>
+        <f>SUM(E3:E3)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F4" s="2" t="e">
-        <f>C4/$L$5*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="e">
-        <f>G4/L4*100</f>
-        <v>#DIV/0!</v>
-      </c>
+        <f>SUM(F3:F3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G4" s="2">
+        <f>SUM(G3:G3)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="2"/>
       <c r="I4" s="2" t="e">
-        <f>G4/$G$5*100</f>
+        <f>SUM(I3:I3)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J4" s="2" t="e">
-        <f>G4/$L$5*100</f>
+        <f>SUM(J3:J3)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K4" s="2" t="e">
-        <f t="shared" ref="K4" si="0">F4+J4</f>
+        <f>SUM(K3:K3)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L4" s="2">
-        <f t="shared" ref="L4" si="1">C4+G4</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="e">
-        <f t="shared" ref="M4" si="2">H4-D4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N4" s="2" t="e">
-        <f t="shared" ref="N4" si="3">C4/G4</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C5" s="2">
-        <f>SUM(C3:C4)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="e">
-        <f>SUM(E3:E4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F5" s="2" t="e">
-        <f>SUM(F3:F4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="2">
-        <f>SUM(G3:G4)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="e">
-        <f>SUM(I3:I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J5" s="2" t="e">
-        <f>SUM(J3:J4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K5" s="2" t="e">
-        <f>SUM(K3:K4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L5" s="2">
-        <f>SUM(L3:L4)</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+        <f>SUM(L3:L3)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="5"/>
-      <c r="D8" s="4">
+      <c r="C7" s="5"/>
+      <c r="D7" s="4">
         <f>C3</f>
         <v>0</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E7" s="4">
         <f>G3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C9" s="5"/>
-      <c r="D9" s="4">
-        <f>C4</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <f>G4</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E92A5B56-DB5A-46DF-8E16-0832CD750F95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="B2:N27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -25940,7 +24889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37FEACAE-0F04-4B00-90FD-3680E5C2B8B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="B3:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -26342,11 +25291,11 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783FC99C-1EEA-41D2-91B9-1F630D5D3A46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="B2:N29"/>
+  <dimension ref="B2:N25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -26404,11 +25353,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E3" s="2" t="e">
-        <f>C3/$C$15*100</f>
+        <f>C3/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F3" s="2" t="e">
-        <f>C3/$L$15*100</f>
+        <f>C3/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="2"/>
@@ -26417,11 +25366,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I3" s="2" t="e">
-        <f>G3/$G$15*100</f>
+        <f>G3/$G$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J3" s="2" t="e">
-        <f>G3/$L$15*100</f>
+        <f>G3/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K3" s="2" t="e">
@@ -26447,44 +25396,44 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="e">
-        <f t="shared" ref="D4:D14" si="0">C4/L4*100</f>
+        <f t="shared" ref="D4:D12" si="0">C4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E4" s="2" t="e">
-        <f t="shared" ref="E4:E14" si="1">C4/$C$15*100</f>
+        <f>C4/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F4" s="2" t="e">
-        <f t="shared" ref="F4:F14" si="2">C4/$L$15*100</f>
+        <f>C4/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="e">
-        <f t="shared" ref="H4:H14" si="3">G4/L4*100</f>
+        <f t="shared" ref="H4:H12" si="1">G4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I4" s="2" t="e">
-        <f t="shared" ref="I4:I14" si="4">G4/$G$15*100</f>
+        <f>G4/$G$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J4" s="2" t="e">
-        <f t="shared" ref="J4:J14" si="5">G4/$L$15*100</f>
+        <f>G4/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K4" s="2" t="e">
-        <f t="shared" ref="K4:K14" si="6">F4+J4</f>
+        <f t="shared" ref="K4:K12" si="2">F4+J4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L4" s="2">
-        <f t="shared" ref="L4:L14" si="7">C4+G4</f>
+        <f t="shared" ref="L4:L12" si="3">C4+G4</f>
         <v>0</v>
       </c>
       <c r="M4" s="2" t="e">
-        <f t="shared" ref="M4:M14" si="8">H4-D4</f>
+        <f t="shared" ref="M4:M12" si="4">H4-D4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N4" s="2" t="e">
-        <f t="shared" ref="N4:N14" si="9">C4/G4</f>
+        <f t="shared" ref="N4:N12" si="5">C4/G4</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26498,40 +25447,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E5" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C5/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F5" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C5/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I5" s="2" t="e">
+        <f>G5/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J5" s="2" t="e">
+        <f>G5/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K5" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L5" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I5" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J5" s="2" t="e">
+      <c r="N5" s="2" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K5" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L5" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="2" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26545,40 +25494,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E6" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C6/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F6" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C6/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I6" s="2" t="e">
+        <f>G6/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J6" s="2" t="e">
+        <f>G6/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K6" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L6" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I6" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J6" s="2" t="e">
+      <c r="N6" s="2" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K6" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L6" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="2" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26592,40 +25541,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E7" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C7/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F7" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C7/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I7" s="2" t="e">
+        <f>G7/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J7" s="2" t="e">
+        <f>G7/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K7" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L7" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I7" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J7" s="2" t="e">
+      <c r="N7" s="2" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K7" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L7" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="2" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26639,40 +25588,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E8" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C8/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F8" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C8/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I8" s="2" t="e">
+        <f>G8/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J8" s="2" t="e">
+        <f>G8/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K8" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L8" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I8" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J8" s="2" t="e">
+      <c r="N8" s="2" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K8" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="2" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26686,40 +25635,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E9" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C9/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F9" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C9/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I9" s="2" t="e">
+        <f>G9/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="2" t="e">
+        <f>G9/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K9" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L9" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I9" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="2" t="e">
+      <c r="N9" s="2" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K9" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L9" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N9" s="2" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26733,40 +25682,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E10" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C10/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F10" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C10/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I10" s="2" t="e">
+        <f>G10/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J10" s="2" t="e">
+        <f>G10/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K10" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L10" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I10" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J10" s="2" t="e">
+      <c r="N10" s="2" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K10" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L10" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10" s="2" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26780,40 +25729,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E11" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C11/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F11" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C11/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I11" s="2" t="e">
+        <f>G11/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J11" s="2" t="e">
+        <f>G11/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K11" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L11" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I11" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J11" s="2" t="e">
+      <c r="N11" s="2" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K11" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L11" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="2" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26827,336 +25776,216 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E12" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C12/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F12" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C12/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I12" s="2" t="e">
+        <f>G12/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J12" s="2" t="e">
+        <f>G12/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K12" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L12" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I12" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J12" s="2" t="e">
+      <c r="N12" s="2" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K12" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L12" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C13" s="2">
+        <f>SUM(C3:C12)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>SUM(E3:E12)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F13" s="2" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
+        <f>SUM(F3:F12)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="2">
+        <f>SUM(G3:G12)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f>SUM(I3:I12)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J13" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f>SUM(J3:J12)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K13" s="2" t="e">
-        <f t="shared" si="6"/>
+        <f>SUM(K3:K12)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L13" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N13" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E14" s="2" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F14" s="2" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I14" s="2" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J14" s="2" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K14" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L14" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N14" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+        <f>SUM(L3:L12)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C15" s="2">
-        <f>SUM(C3:C14)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2" t="e">
-        <f>SUM(E3:E14)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" s="2" t="e">
-        <f>SUM(F3:F14)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="2">
-        <f>SUM(G3:G14)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2" t="e">
-        <f>SUM(I3:I14)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J15" s="2" t="e">
-        <f>SUM(J3:J14)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K15" s="2" t="e">
-        <f>SUM(K3:K14)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L15" s="2">
-        <f>SUM(L3:L14)</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="D15" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C16" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <f>C3</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <f>G3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>16</v>
+      <c r="C17" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <f>G4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C18" s="10" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <f>C3</f>
+        <f>C5</f>
         <v>0</v>
       </c>
       <c r="E18" s="2">
-        <f>G3</f>
+        <f>G5</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C19" s="10" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" ref="D19:D29" si="10">C4</f>
+        <f>C6</f>
         <v>0</v>
       </c>
       <c r="E19" s="2">
-        <f t="shared" ref="E19:E29" si="11">G4</f>
+        <f>G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="10"/>
+        <f>C7</f>
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <f t="shared" si="11"/>
+        <f>G7</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C21" s="10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="10"/>
+        <f>C8</f>
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <f t="shared" si="11"/>
+        <f>G8</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C22" s="10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" si="10"/>
+        <f>C9</f>
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <f t="shared" si="11"/>
+        <f>G9</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C23" s="10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="10"/>
+        <f>C10</f>
         <v>0</v>
       </c>
       <c r="E23" s="2">
-        <f t="shared" si="11"/>
+        <f>G10</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C24" s="10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="10"/>
+        <f>C11</f>
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <f t="shared" si="11"/>
+        <f>G11</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C25" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2">
-        <f t="shared" si="10"/>
+        <f>C12</f>
         <v>0</v>
       </c>
       <c r="E25" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C26" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C27" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E27" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C28" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E28" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="2">
-        <f t="shared" si="11"/>
+        <f>G12</f>
         <v>0</v>
       </c>
     </row>
@@ -27167,7 +25996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6FCAD0-422D-4907-A16C-08BB26CF5380}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -27221,7 +26050,7 @@
     </row>
     <row r="3" spans="2:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="e">
@@ -27268,7 +26097,7 @@
     </row>
     <row r="4" spans="2:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="e">
@@ -27315,7 +26144,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="e">
@@ -27362,7 +26191,7 @@
     </row>
     <row r="6" spans="2:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="e">
@@ -27409,7 +26238,7 @@
     </row>
     <row r="7" spans="2:14" ht="39" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="e">
@@ -27502,7 +26331,7 @@
     </row>
     <row r="12" spans="2:14" ht="39" x14ac:dyDescent="0.25">
       <c r="C12" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2">
         <f>C3</f>
@@ -27515,7 +26344,7 @@
     </row>
     <row r="13" spans="2:14" ht="39" x14ac:dyDescent="0.25">
       <c r="C13" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D13" s="2">
         <f t="shared" ref="D13:D16" si="6">C4</f>
@@ -27528,7 +26357,7 @@
     </row>
     <row r="14" spans="2:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="C14" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="6"/>
@@ -27541,7 +26370,7 @@
     </row>
     <row r="15" spans="2:14" ht="51" x14ac:dyDescent="0.25">
       <c r="C15" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="6"/>
@@ -27554,7 +26383,7 @@
     </row>
     <row r="16" spans="2:14" ht="51.75" x14ac:dyDescent="0.25">
       <c r="C16" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="6"/>
@@ -27572,8 +26401,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CC4B3F-EE28-4A6F-8F60-E3418A65B7A9}">
-  <dimension ref="B2:N32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B2:N26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
@@ -27633,11 +26462,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E3" s="18" t="e">
-        <f t="shared" ref="E3:E14" si="0">C3/$C$16*100</f>
+        <f>C3/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F3" s="18" t="e">
-        <f t="shared" ref="F3:F14" si="1">C3/$L$16*100</f>
+        <f>C3/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="17"/>
@@ -27646,11 +26475,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I3" s="18" t="e">
-        <f t="shared" ref="I3:I14" si="2">G3/$G$16*100</f>
+        <f>G3/$G$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J3" s="18" t="e">
-        <f t="shared" ref="J3:J14" si="3">G3/$L$16*100</f>
+        <f>G3/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K3" s="18" t="e">
@@ -27676,44 +26505,44 @@
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="18" t="e">
-        <f t="shared" ref="D4:D15" si="4">C4/L4*100</f>
+        <f t="shared" ref="D4:D11" si="0">C4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E4" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C4/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F4" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C4/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="18" t="e">
-        <f t="shared" ref="H4:H15" si="5">G4/L4*100</f>
+        <f t="shared" ref="H4:H11" si="1">G4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I4" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f>G4/$G$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J4" s="18" t="e">
-        <f t="shared" si="3"/>
+        <f>G4/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K4" s="18" t="e">
-        <f t="shared" ref="K4:K15" si="6">F4+J4</f>
+        <f t="shared" ref="K4:K11" si="2">F4+J4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L4" s="19">
-        <f t="shared" ref="L4:L15" si="7">C4+G4</f>
+        <f t="shared" ref="L4:L11" si="3">C4+G4</f>
         <v>0</v>
       </c>
       <c r="M4" s="18" t="e">
-        <f t="shared" ref="M4:M15" si="8">H4-D4</f>
+        <f t="shared" ref="M4:M11" si="4">H4-D4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N4" s="19" t="e">
-        <f t="shared" ref="N4:N15" si="9">C4/G4</f>
+        <f t="shared" ref="N4:N11" si="5">C4/G4</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -27723,44 +26552,44 @@
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E5" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C5/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F5" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C5/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I5" s="18" t="e">
+        <f>G5/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J5" s="18" t="e">
+        <f>G5/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K5" s="18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L5" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="19" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I5" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J5" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K5" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L5" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="19" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -27770,44 +26599,44 @@
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E6" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C6/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F6" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C6/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I6" s="18" t="e">
+        <f>G6/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J6" s="18" t="e">
+        <f>G6/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K6" s="18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L6" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="19" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I6" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J6" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K6" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L6" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="19" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -27817,44 +26646,44 @@
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E7" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C7/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F7" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C7/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I7" s="18" t="e">
+        <f>G7/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J7" s="18" t="e">
+        <f>G7/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K7" s="18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L7" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="19" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I7" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J7" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K7" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L7" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="19" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -27864,44 +26693,44 @@
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E8" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C8/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F8" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C8/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I8" s="18" t="e">
+        <f>G8/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J8" s="18" t="e">
+        <f>G8/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K8" s="18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L8" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="19" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I8" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J8" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K8" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="19" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -27911,44 +26740,44 @@
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E9" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C9/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F9" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C9/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I9" s="18" t="e">
+        <f>G9/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="18" t="e">
+        <f>G9/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K9" s="18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L9" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="19" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I9" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J9" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K9" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L9" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N9" s="19" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -27958,44 +26787,44 @@
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E10" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C10/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F10" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C10/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I10" s="18" t="e">
+        <f>G10/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J10" s="18" t="e">
+        <f>G10/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K10" s="18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L10" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="19" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I10" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J10" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K10" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L10" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10" s="19" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -28005,50 +26834,50 @@
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E11" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C11/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F11" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C11/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I11" s="18" t="e">
+        <f>G11/$G$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J11" s="18" t="e">
+        <f>G11/$L$13*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K11" s="18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L11" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="19" t="e">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I11" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J11" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K11" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L11" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="19" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="16" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="18" t="e">
@@ -28056,11 +26885,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E12" s="18" t="e">
-        <f t="shared" si="0"/>
+        <f>C12/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F12" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f>C12/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G12" s="17"/>
@@ -28069,11 +26898,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I12" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f>G12/$G$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J12" s="18" t="e">
-        <f t="shared" si="3"/>
+        <f>G12/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K12" s="18" t="e">
@@ -28094,345 +26923,183 @@
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E13" s="18" t="e">
-        <f t="shared" si="0"/>
+      <c r="C13" s="20">
+        <f>SUM(C3:C12)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21" t="e">
+        <f>SUM(E3:E12)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F13" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I13" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f>SUM(F3:F12)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="20">
+        <f>SUM(G3:G12)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21" t="e">
+        <f>SUM(I3:I12)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J13" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K13" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L13" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
+        <f>SUM(J3:J12)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K13" s="21" t="e">
+        <f>SUM(K3:K12)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L13" s="20">
+        <f>SUM(L3:L12)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="21"/>
       <c r="N13" s="19" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E14" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F14" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I14" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J14" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K14" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L14" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N14" s="19" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E15" s="18" t="e">
-        <f>C15/$C$16*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" s="18" t="e">
-        <f>C15/$L$16*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I15" s="18" t="e">
-        <f>G15/$G$16*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J15" s="18" t="e">
-        <f>G15/$L$16*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K15" s="18" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L15" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N15" s="19" t="e">
-        <f t="shared" si="9"/>
+        <f>C13/G13</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="20">
-        <f>SUM(C3:C15)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21" t="e">
-        <f>SUM(E3:E15)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="18" t="e">
-        <f>SUM(F3:F15)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G16" s="20">
-        <f>SUM(G3:G15)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21" t="e">
-        <f>SUM(I3:I15)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J16" s="18" t="e">
-        <f>SUM(J3:J15)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K16" s="21" t="e">
-        <f>SUM(K3:K15)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L16" s="20">
-        <f>SUM(L3:L15)</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="21"/>
-      <c r="N16" s="19" t="e">
-        <f>C16/G16</f>
-        <v>#DIV/0!</v>
+      <c r="D16" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="21">
+        <f>C3</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="21">
+        <f>G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="21">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="21">
+        <f>G4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>16</v>
+      <c r="C19" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="21">
+        <f>C5</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="21">
+        <f>G5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C20" s="16" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20" s="21">
-        <f t="shared" ref="D20:D28" si="10">C3</f>
+        <f>C6</f>
         <v>0</v>
       </c>
       <c r="E20" s="21">
-        <f t="shared" ref="E20:E28" si="11">G3</f>
+        <f>G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C21" s="16" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" s="21">
-        <f t="shared" si="10"/>
+        <f>C7</f>
         <v>0</v>
       </c>
       <c r="E21" s="21">
-        <f t="shared" si="11"/>
+        <f>G7</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C22" s="16" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" s="21">
-        <f t="shared" si="10"/>
+        <f>C8</f>
         <v>0</v>
       </c>
       <c r="E22" s="21">
-        <f t="shared" si="11"/>
+        <f>G8</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C23" s="16" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="21">
-        <f t="shared" si="10"/>
+        <f>C9</f>
         <v>0</v>
       </c>
       <c r="E23" s="21">
-        <f t="shared" si="11"/>
+        <f>G9</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C24" s="16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D24" s="21">
-        <f t="shared" si="10"/>
+        <f>C10</f>
         <v>0</v>
       </c>
       <c r="E24" s="21">
-        <f t="shared" si="11"/>
+        <f>G10</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C25" s="16" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" s="21">
-        <f t="shared" si="10"/>
+        <f>C11</f>
         <v>0</v>
       </c>
       <c r="E25" s="21">
-        <f t="shared" si="11"/>
+        <f>G11</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C26" s="16" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D26" s="21">
-        <f t="shared" si="10"/>
+        <f>C12</f>
         <v>0</v>
       </c>
       <c r="E26" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C27" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E27" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C28" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E28" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C29" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="21">
-        <f t="shared" ref="D29" si="12">C15</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="21">
-        <f t="shared" ref="E29" si="13">G15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C30" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C31" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C32" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+        <f>G12</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28441,7 +27108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2810FB87-04BA-4D77-A588-53EFE8E087C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -28785,7 +27452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1776768B-CE21-43B7-B2BF-5FA02C88CFB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -28888,7 +27555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{474E76DE-E3AE-4F4F-80ED-C288F43D3FB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -28990,7 +27657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5BBC813-5B1C-46E7-8C50-6C3399ED308C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -29815,7 +28482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A03669-A941-4F47-81D7-CA28039D4EAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -29868,7 +28535,7 @@
     </row>
     <row r="3" spans="2:14" ht="39" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="e">
@@ -29915,7 +28582,7 @@
     </row>
     <row r="4" spans="2:14" ht="39" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="e">
@@ -29962,7 +28629,7 @@
     </row>
     <row r="5" spans="2:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="e">
@@ -30009,7 +28676,7 @@
     </row>
     <row r="6" spans="2:14" ht="51" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="e">
@@ -30056,7 +28723,7 @@
     </row>
     <row r="7" spans="2:14" ht="51.75" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="e">
@@ -30149,7 +28816,7 @@
     </row>
     <row r="11" spans="2:14" ht="39" x14ac:dyDescent="0.25">
       <c r="C11" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11" s="2">
         <f>C3</f>
@@ -30162,7 +28829,7 @@
     </row>
     <row r="12" spans="2:14" ht="39" x14ac:dyDescent="0.25">
       <c r="C12" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" ref="D12:D15" si="6">C4</f>
@@ -30175,7 +28842,7 @@
     </row>
     <row r="13" spans="2:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="C13" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D13" s="2">
         <f t="shared" si="6"/>
@@ -30188,7 +28855,7 @@
     </row>
     <row r="14" spans="2:14" ht="51" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="6"/>
@@ -30201,7 +28868,7 @@
     </row>
     <row r="15" spans="2:14" ht="51.75" x14ac:dyDescent="0.25">
       <c r="C15" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="6"/>
@@ -30219,7 +28886,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4695981-694D-4635-9D7F-D10F3EFBBD44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -30563,7 +29230,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E2A3BC-18E5-4FB4-BBB6-EC4EE7CA082D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -31228,7 +29895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B56C3CC-1EDF-4F25-93FB-27C0C2978B0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -31823,7 +30490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC656725-F70A-477D-9822-CF7AA211AEA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -32286,7 +30953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D135A86D-A449-4741-8BDC-ADBF7E0CCB21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -32420,7 +31087,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5CFE1D-121F-4F4C-8FBC-CDE13DB23FC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -32471,7 +31138,7 @@
     </row>
     <row r="3" spans="2:14" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B3" s="32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25" t="e">
@@ -32518,7 +31185,7 @@
     </row>
     <row r="4" spans="2:14" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25" t="e">
@@ -32565,7 +31232,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="25" t="e">
@@ -32612,7 +31279,7 @@
     </row>
     <row r="6" spans="2:14" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="25" t="e">
@@ -32659,7 +31326,7 @@
     </row>
     <row r="7" spans="2:14" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="25" t="e">
@@ -32795,7 +31462,7 @@
     <row r="12" spans="2:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="B12" s="30"/>
       <c r="C12" s="32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="21">
         <f>C3</f>
@@ -32818,7 +31485,7 @@
     <row r="13" spans="2:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="B13" s="30"/>
       <c r="C13" s="32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D13" s="21">
         <f>C4</f>
@@ -32841,7 +31508,7 @@
     <row r="14" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B14" s="30"/>
       <c r="C14" s="32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" s="21">
         <f>C5</f>
@@ -32864,7 +31531,7 @@
     <row r="15" spans="2:14" ht="42.75" x14ac:dyDescent="0.3">
       <c r="B15" s="30"/>
       <c r="C15" s="29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D15" s="21">
         <f>C6</f>
@@ -32887,7 +31554,7 @@
     <row r="16" spans="2:14" ht="43.5" x14ac:dyDescent="0.3">
       <c r="B16" s="30"/>
       <c r="C16" s="32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D16" s="21">
         <f>C7</f>
@@ -32914,7 +31581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9E4E088-48B2-4EF9-91BD-3B2B92FC43CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:N13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -33257,7 +31924,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2001324-55AD-4441-A471-B1EB25319396}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -33358,7 +32025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEC48CF4-8D52-46FA-A968-8D88C171F5D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -33457,7 +32124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A2B5179-7E86-4CCB-B70D-0EBC5EBE7154}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B2:N8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Igualdad/cuadro_porcentajes/CUADRO_PORCENTAJES.xlsx
+++ b/Igualdad/cuadro_porcentajes/CUADRO_PORCENTAJES.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Igualdad\cuadro_porcentajes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62280010-6084-403F-9725-97D94C2AD094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="9" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="TOTAL PLANTILLA" sheetId="27" r:id="rId1"/>
@@ -41,7 +40,7 @@
     <sheet name="PUESTOS DIRECTIVOS PERSONAL SUB" sheetId="25" r:id="rId26"/>
     <sheet name="PUESTOS PROF. PERSONAL SUBROGAD" sheetId="26" r:id="rId27"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -65,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="100">
   <si>
     <t>Menos de 20 años</t>
   </si>
@@ -357,11 +356,20 @@
   <si>
     <t>más 60 años</t>
   </si>
+  <si>
+    <t>Otros</t>
+  </si>
+  <si>
+    <t>Matrimonio</t>
+  </si>
+  <si>
+    <t>Hospitalizacion de familiares</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -493,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -579,6 +587,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,6 +842,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -840,7 +850,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -931,7 +940,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>EXCEDENCIAS!$D$8</c:f>
+              <c:f>EXCEDENCIAS!$D$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -952,7 +961,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>EXCEDENCIAS!$C$9:$C$11</c:f>
+              <c:f>EXCEDENCIAS!$C$10:$C$12</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -969,7 +978,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>EXCEDENCIAS!$D$9:$D$11</c:f>
+              <c:f>EXCEDENCIAS!$D$10:$D$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -996,7 +1005,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>EXCEDENCIAS!$E$8</c:f>
+              <c:f>EXCEDENCIAS!$E$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1017,7 +1026,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>EXCEDENCIAS!$C$9:$C$11</c:f>
+              <c:f>EXCEDENCIAS!$C$10:$C$12</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1034,7 +1043,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>EXCEDENCIAS!$E$9:$E$11</c:f>
+              <c:f>EXCEDENCIAS!$E$10:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1217,6 +1226,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1224,7 +1234,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1274,6 +1283,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1315,7 +1325,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'PERMISOS RETRIBUIDOS'!$C$8</c:f>
+              <c:f>'PERMISOS RETRIBUIDOS'!$C$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1336,7 +1346,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'PERMISOS RETRIBUIDOS'!$D$7:$E$7</c:f>
+              <c:f>'PERMISOS RETRIBUIDOS'!$D$10:$E$10</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -1350,7 +1360,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PERMISOS RETRIBUIDOS'!$D$8:$E$8</c:f>
+              <c:f>'PERMISOS RETRIBUIDOS'!$D$11:$E$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1374,7 +1384,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'PERMISOS RETRIBUIDOS'!$C$9</c:f>
+              <c:f>'PERMISOS RETRIBUIDOS'!$C$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1395,7 +1405,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'PERMISOS RETRIBUIDOS'!$D$7:$E$7</c:f>
+              <c:f>'PERMISOS RETRIBUIDOS'!$D$10:$E$10</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -1409,7 +1419,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PERMISOS RETRIBUIDOS'!$D$9:$E$9</c:f>
+              <c:f>'PERMISOS RETRIBUIDOS'!$D$12:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1558,6 +1568,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1589,6 +1600,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1596,7 +1608,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2069,6 +2080,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2076,7 +2088,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2477,6 +2488,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2484,7 +2496,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3345,6 +3356,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3352,7 +3364,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3741,6 +3752,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3748,7 +3760,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4233,6 +4244,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4240,7 +4252,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4641,6 +4652,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4648,7 +4660,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5037,6 +5048,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5044,7 +5056,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5558,6 +5569,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5565,7 +5577,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5968,6 +5979,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5975,7 +5987,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6318,6 +6329,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6325,7 +6337,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6797,6 +6808,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6804,7 +6816,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7593,6 +7604,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7600,7 +7612,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7989,6 +8000,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7996,7 +8008,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8385,6 +8396,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8392,7 +8404,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8781,6 +8792,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8788,7 +8800,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9201,6 +9212,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9208,7 +9220,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -20805,13 +20816,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>166687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>52387</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -21579,13 +21590,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>128587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -21910,7 +21921,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21999,7 +22010,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:N15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22340,7 +22351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22681,7 +22692,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23470,8 +23481,8 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="B2:N11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -23528,11 +23539,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E3" s="2" t="e">
-        <f>C3/$C$6*100</f>
+        <f>C3/$C$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F3" s="2" t="e">
-        <f>C3/$L$6*100</f>
+        <f>C3/$L$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="2"/>
@@ -23541,11 +23552,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I3" s="2" t="e">
-        <f>G3/$G$6*100</f>
+        <f>G3/$G$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J3" s="2" t="e">
-        <f>G3/$L$6*100</f>
+        <f>G3/$L$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K3" s="2" t="e">
@@ -23575,40 +23586,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E4" s="2" t="e">
-        <f t="shared" ref="E4:E5" si="1">C4/$C$6*100</f>
+        <f>C4/$C$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F4" s="2" t="e">
-        <f t="shared" ref="F4:F5" si="2">C4/$L$6*100</f>
+        <f>C4/$L$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="e">
-        <f t="shared" ref="H4:H5" si="3">G4/L4*100</f>
+        <f t="shared" ref="H4:H5" si="1">G4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I4" s="2" t="e">
-        <f t="shared" ref="I4:I5" si="4">G4/$G$6*100</f>
+        <f>G4/$G$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J4" s="2" t="e">
-        <f t="shared" ref="J4:J5" si="5">G4/$L$6*100</f>
+        <f>G4/$L$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K4" s="2" t="e">
-        <f t="shared" ref="K4:K5" si="6">F4+J4</f>
+        <f t="shared" ref="K4:K5" si="2">F4+J4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L4" s="2">
-        <f t="shared" ref="L4:L5" si="7">C4+G4</f>
+        <f t="shared" ref="L4:L5" si="3">C4+G4</f>
         <v>0</v>
       </c>
       <c r="M4" s="2" t="e">
-        <f t="shared" ref="M4:M5" si="8">H4-D4</f>
+        <f t="shared" ref="M4:M5" si="4">H4-D4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N4" s="2" t="e">
-        <f t="shared" ref="N4:N5" si="9">C4/G4</f>
+        <f t="shared" ref="N4:N5" si="5">C4/G4</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -23622,140 +23633,189 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E5" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>C5/$C$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F5" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>C5/$L$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I5" s="2" t="e">
+        <f>G5/$G$7*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J5" s="2" t="e">
+        <f>G5/$L$7*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K5" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L5" s="2">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I5" s="2" t="e">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J5" s="2" t="e">
+      <c r="N5" s="2" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K5" s="2" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L5" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C6" s="2">
-        <f>SUM(C3:C5)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="B6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="e">
+        <f t="shared" ref="D6" si="6">C6/L6*100</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="E6" s="2" t="e">
-        <f>SUM(E3:E5)</f>
+        <f>C6/$C$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F6" s="2" t="e">
-        <f>SUM(F3:F5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G6" s="2">
-        <f>SUM(G3:G5)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="2"/>
+        <f>C6/$L$7*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="e">
+        <f t="shared" ref="H6" si="7">G6/L6*100</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="I6" s="2" t="e">
-        <f>SUM(I3:I5)</f>
+        <f>G6/$G$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J6" s="2" t="e">
-        <f>SUM(J3:J5)</f>
+        <f>G6/$L$7*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K6" s="2" t="e">
-        <f>SUM(K3:K5)</f>
+        <f t="shared" ref="K6" si="8">F6+J6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L6" s="2">
-        <f>SUM(L3:L5)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D8" s="12" t="s">
+        <f t="shared" ref="L6" si="9">C6+G6</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="e">
+        <f t="shared" ref="M6" si="10">H6-D6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="2" t="e">
+        <f t="shared" ref="N6" si="11">C6/G6</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C7" s="2">
+        <f>SUM(C3:C6)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="e">
+        <f>SUM(E3:E6)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F7" s="2" t="e">
+        <f>SUM(F3:F6)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G7" s="2">
+        <f>SUM(G3:G6)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="e">
+        <f>SUM(I3:I6)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J7" s="2" t="e">
+        <f>SUM(J3:J6)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K7" s="2" t="e">
+        <f>SUM(K3:K6)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L7" s="2">
+        <f>SUM(L3:L6)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="C9" s="5" t="s">
+    <row r="10" spans="2:14" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="C10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D10" s="4">
         <f>C3</f>
         <v>0</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E10" s="4">
         <f>G3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="39" x14ac:dyDescent="0.25">
-      <c r="C10" s="5" t="s">
+    <row r="11" spans="2:14" ht="39" x14ac:dyDescent="0.25">
+      <c r="C11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="4">
-        <f t="shared" ref="D10:D11" si="10">C4</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <f t="shared" ref="E10:E11" si="11">G4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="4">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <f>G4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="C12" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <f t="shared" si="11"/>
+      <c r="D12" s="4">
+        <f t="shared" ref="D12" si="12">C5</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" ref="E12" si="13">G5</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="B2:N9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="45" x14ac:dyDescent="0.25">
@@ -23809,11 +23869,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E3" s="2" t="e">
-        <f>C3/$C$5*100</f>
+        <f>C3/$C$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F3" s="2" t="e">
-        <f>C3/$L$5*100</f>
+        <f>C3/$L$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="2"/>
@@ -23822,11 +23882,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I3" s="2" t="e">
-        <f>G3/$G$5*100</f>
+        <f>G3/$G$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J3" s="2" t="e">
-        <f>G3/$L$5*100</f>
+        <f>G3/$L$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K3" s="2" t="e">
@@ -23856,11 +23916,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E4" s="2" t="e">
-        <f>C4/$C$5*100</f>
+        <f>C4/$C$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F4" s="2" t="e">
-        <f>C4/$L$5*100</f>
+        <f>C4/$L$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G4" s="2"/>
@@ -23869,11 +23929,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I4" s="2" t="e">
-        <f>G4/$G$5*100</f>
+        <f>G4/$G$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J4" s="2" t="e">
-        <f>G4/$L$5*100</f>
+        <f>G4/$L$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K4" s="2" t="e">
@@ -23894,74 +23954,215 @@
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C5" s="2">
-        <f>SUM(C3:C4)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="B5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="e">
+        <f>C5/L5*100</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="E5" s="2" t="e">
-        <f>SUM(E3:E4)</f>
+        <f>C5/$C$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F5" s="2" t="e">
-        <f>SUM(F3:F4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="2">
-        <f>SUM(G3:G4)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="2"/>
+        <f>C5/$L$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="e">
+        <f>G5/L5*100</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="I5" s="2" t="e">
-        <f>SUM(I3:I4)</f>
+        <f>G5/$G$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J5" s="2" t="e">
-        <f>SUM(J3:J4)</f>
+        <f>G5/$L$8*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K5" s="2" t="e">
-        <f>SUM(K3:K4)</f>
+        <f>F5+J5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L5" s="2">
-        <f>SUM(L3:L4)</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+        <f>C5+G5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="e">
+        <f>H5-D5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="2" t="e">
+        <f>C5/G5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="39" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="e">
+        <f>C6/L6*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E6" s="2" t="e">
+        <f>C6/$C$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F6" s="2" t="e">
+        <f>C6/$L$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="e">
+        <f>G6/L6*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I6" s="2" t="e">
+        <f>G6/$G$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J6" s="2" t="e">
+        <f>G6/$L$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K6" s="2" t="e">
+        <f t="shared" ref="K6" si="4">F6+J6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L6" s="2">
+        <f t="shared" ref="L6" si="5">C6+G6</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="e">
+        <f t="shared" ref="M6" si="6">H6-D6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="2" t="e">
+        <f t="shared" ref="N6" si="7">C6/G6</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D7" s="12" t="s">
+      <c r="B7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="e">
+        <f>C7/L7*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E7" s="2" t="e">
+        <f>C7/$C$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F7" s="2" t="e">
+        <f>C7/$L$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="e">
+        <f>G7/L7*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I7" s="2" t="e">
+        <f>G7/$G$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J7" s="2" t="e">
+        <f>G7/$L$8*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K7" s="2" t="e">
+        <f t="shared" ref="K7" si="8">F7+J7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L7" s="2">
+        <f t="shared" ref="L7" si="9">C7+G7</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="e">
+        <f t="shared" ref="M7" si="10">H7-D7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="2" t="e">
+        <f t="shared" ref="N7" si="11">C7/G7</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C8" s="35">
+        <f>SUM(C3:C7)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="e">
+        <f>SUM(E3:E7)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F8" s="2" t="e">
+        <f>SUM(F3:F7)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="2">
+        <f>SUM(G3:G7)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="e">
+        <f>SUM(I3:I7)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J8" s="2" t="e">
+        <f>SUM(J3:J7)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K8" s="2" t="e">
+        <f>SUM(K3:K7)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L8" s="2">
+        <f>SUM(L3:L7)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="5" t="s">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="4">
-        <f>C3</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
-        <f>G3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C9" s="5" t="s">
+      <c r="D11" s="4">
+        <f>C5</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <f>G5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="4">
-        <f>C4</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <f>G4</f>
+      <c r="D12" s="4">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <f>G7</f>
         <v>0</v>
       </c>
     </row>
@@ -23972,7 +24173,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24128,7 +24329,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24889,7 +25090,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -25291,7 +25492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -25353,11 +25554,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E3" s="2" t="e">
-        <f>C3/$C$13*100</f>
+        <f t="shared" ref="E3:E12" si="0">C3/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F3" s="2" t="e">
-        <f>C3/$L$13*100</f>
+        <f t="shared" ref="F3:F12" si="1">C3/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="2"/>
@@ -25366,11 +25567,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I3" s="2" t="e">
-        <f>G3/$G$13*100</f>
+        <f t="shared" ref="I3:I12" si="2">G3/$G$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J3" s="2" t="e">
-        <f>G3/$L$13*100</f>
+        <f t="shared" ref="J3:J12" si="3">G3/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K3" s="2" t="e">
@@ -25396,44 +25597,44 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="e">
-        <f t="shared" ref="D4:D12" si="0">C4/L4*100</f>
+        <f t="shared" ref="D4:D12" si="4">C4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E4" s="2" t="e">
-        <f>C4/$C$13*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F4" s="2" t="e">
-        <f>C4/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="e">
-        <f t="shared" ref="H4:H12" si="1">G4/L4*100</f>
+        <f t="shared" ref="H4:H12" si="5">G4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I4" s="2" t="e">
-        <f>G4/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J4" s="2" t="e">
-        <f>G4/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K4" s="2" t="e">
-        <f t="shared" ref="K4:K12" si="2">F4+J4</f>
+        <f t="shared" ref="K4:K12" si="6">F4+J4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L4" s="2">
-        <f t="shared" ref="L4:L12" si="3">C4+G4</f>
+        <f t="shared" ref="L4:L12" si="7">C4+G4</f>
         <v>0</v>
       </c>
       <c r="M4" s="2" t="e">
-        <f t="shared" ref="M4:M12" si="4">H4-D4</f>
+        <f t="shared" ref="M4:M12" si="8">H4-D4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N4" s="2" t="e">
-        <f t="shared" ref="N4:N12" si="5">C4/G4</f>
+        <f t="shared" ref="N4:N12" si="9">C4/G4</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25443,44 +25644,44 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E5" s="2" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E5" s="2" t="e">
-        <f>C5/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F5" s="2" t="e">
-        <f>C5/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I5" s="2" t="e">
-        <f>G5/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J5" s="2" t="e">
-        <f>G5/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K5" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L5" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M5" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N5" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25490,44 +25691,44 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E6" s="2" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E6" s="2" t="e">
-        <f>C6/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F6" s="2" t="e">
-        <f>C6/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I6" s="2" t="e">
-        <f>G6/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J6" s="2" t="e">
-        <f>G6/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K6" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L6" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M6" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N6" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25537,44 +25738,44 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E7" s="2" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E7" s="2" t="e">
-        <f>C7/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F7" s="2" t="e">
-        <f>C7/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I7" s="2" t="e">
-        <f>G7/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J7" s="2" t="e">
-        <f>G7/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K7" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L7" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M7" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N7" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25584,44 +25785,44 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E8" s="2" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E8" s="2" t="e">
-        <f>C8/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F8" s="2" t="e">
-        <f>C8/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I8" s="2" t="e">
-        <f>G8/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J8" s="2" t="e">
-        <f>G8/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K8" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M8" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N8" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25631,44 +25832,44 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E9" s="2" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E9" s="2" t="e">
-        <f>C9/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F9" s="2" t="e">
-        <f>C9/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I9" s="2" t="e">
-        <f>G9/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J9" s="2" t="e">
-        <f>G9/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K9" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L9" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M9" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N9" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25678,44 +25879,44 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E10" s="2" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E10" s="2" t="e">
-        <f>C10/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F10" s="2" t="e">
-        <f>C10/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I10" s="2" t="e">
-        <f>G10/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J10" s="2" t="e">
-        <f>G10/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K10" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M10" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N10" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25725,44 +25926,44 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E11" s="2" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E11" s="2" t="e">
-        <f>C11/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F11" s="2" t="e">
-        <f>C11/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I11" s="2" t="e">
-        <f>G11/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J11" s="2" t="e">
-        <f>G11/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K11" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L11" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M11" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N11" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25772,44 +25973,44 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E12" s="2" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E12" s="2" t="e">
-        <f>C12/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F12" s="2" t="e">
-        <f>C12/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I12" s="2" t="e">
-        <f>G12/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J12" s="2" t="e">
-        <f>G12/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K12" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L12" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M12" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N12" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -25864,11 +26065,11 @@
         <v>0</v>
       </c>
       <c r="D16" s="2">
-        <f>C3</f>
+        <f t="shared" ref="D16:D25" si="10">C3</f>
         <v>0</v>
       </c>
       <c r="E16" s="2">
-        <f>G3</f>
+        <f t="shared" ref="E16:E25" si="11">G3</f>
         <v>0</v>
       </c>
     </row>
@@ -25877,11 +26078,11 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <f>C4</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E17" s="2">
-        <f>G4</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25890,11 +26091,11 @@
         <v>2</v>
       </c>
       <c r="D18" s="2">
-        <f>C5</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E18" s="2">
-        <f>G5</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25903,11 +26104,11 @@
         <v>3</v>
       </c>
       <c r="D19" s="2">
-        <f>C6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E19" s="2">
-        <f>G6</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25916,11 +26117,11 @@
         <v>4</v>
       </c>
       <c r="D20" s="2">
-        <f>C7</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <f>G7</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25929,11 +26130,11 @@
         <v>5</v>
       </c>
       <c r="D21" s="2">
-        <f>C8</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <f>G8</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25942,11 +26143,11 @@
         <v>6</v>
       </c>
       <c r="D22" s="2">
-        <f>C9</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <f>G9</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25955,11 +26156,11 @@
         <v>7</v>
       </c>
       <c r="D23" s="2">
-        <f>C10</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E23" s="2">
-        <f>G10</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25968,11 +26169,11 @@
         <v>8</v>
       </c>
       <c r="D24" s="2">
-        <f>C11</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <f>G11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25981,11 +26182,11 @@
         <v>9</v>
       </c>
       <c r="D25" s="2">
-        <f>C12</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E25" s="2">
-        <f>G12</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -25996,7 +26197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -26401,7 +26602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -26462,11 +26663,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E3" s="18" t="e">
-        <f>C3/$C$13*100</f>
+        <f t="shared" ref="E3:E12" si="0">C3/$C$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F3" s="18" t="e">
-        <f>C3/$L$13*100</f>
+        <f t="shared" ref="F3:F12" si="1">C3/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="17"/>
@@ -26475,11 +26676,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I3" s="18" t="e">
-        <f>G3/$G$13*100</f>
+        <f t="shared" ref="I3:I12" si="2">G3/$G$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J3" s="18" t="e">
-        <f>G3/$L$13*100</f>
+        <f t="shared" ref="J3:J12" si="3">G3/$L$13*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K3" s="18" t="e">
@@ -26505,44 +26706,44 @@
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="18" t="e">
-        <f t="shared" ref="D4:D11" si="0">C4/L4*100</f>
+        <f t="shared" ref="D4:D11" si="4">C4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E4" s="18" t="e">
-        <f>C4/$C$13*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F4" s="18" t="e">
-        <f>C4/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="18" t="e">
-        <f t="shared" ref="H4:H11" si="1">G4/L4*100</f>
+        <f t="shared" ref="H4:H11" si="5">G4/L4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I4" s="18" t="e">
-        <f>G4/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J4" s="18" t="e">
-        <f>G4/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K4" s="18" t="e">
-        <f t="shared" ref="K4:K11" si="2">F4+J4</f>
+        <f t="shared" ref="K4:K11" si="6">F4+J4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L4" s="19">
-        <f t="shared" ref="L4:L11" si="3">C4+G4</f>
+        <f t="shared" ref="L4:L11" si="7">C4+G4</f>
         <v>0</v>
       </c>
       <c r="M4" s="18" t="e">
-        <f t="shared" ref="M4:M11" si="4">H4-D4</f>
+        <f t="shared" ref="M4:M11" si="8">H4-D4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N4" s="19" t="e">
-        <f t="shared" ref="N4:N11" si="5">C4/G4</f>
+        <f t="shared" ref="N4:N11" si="9">C4/G4</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26552,44 +26753,44 @@
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E5" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E5" s="18" t="e">
-        <f>C5/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F5" s="18" t="e">
-        <f>C5/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I5" s="18" t="e">
-        <f>G5/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J5" s="18" t="e">
-        <f>G5/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K5" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L5" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M5" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N5" s="19" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26599,44 +26800,44 @@
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E6" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E6" s="18" t="e">
-        <f>C6/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F6" s="18" t="e">
-        <f>C6/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I6" s="18" t="e">
-        <f>G6/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J6" s="18" t="e">
-        <f>G6/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K6" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L6" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M6" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N6" s="19" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26646,44 +26847,44 @@
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E7" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E7" s="18" t="e">
-        <f>C7/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F7" s="18" t="e">
-        <f>C7/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I7" s="18" t="e">
-        <f>G7/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J7" s="18" t="e">
-        <f>G7/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K7" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L7" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M7" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N7" s="19" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26693,44 +26894,44 @@
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E8" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E8" s="18" t="e">
-        <f>C8/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F8" s="18" t="e">
-        <f>C8/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I8" s="18" t="e">
-        <f>G8/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J8" s="18" t="e">
-        <f>G8/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K8" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L8" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M8" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N8" s="19" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26740,44 +26941,44 @@
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E9" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E9" s="18" t="e">
-        <f>C9/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F9" s="18" t="e">
-        <f>C9/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I9" s="18" t="e">
-        <f>G9/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J9" s="18" t="e">
-        <f>G9/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K9" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M9" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N9" s="19" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26787,44 +26988,44 @@
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E10" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E10" s="18" t="e">
-        <f>C10/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F10" s="18" t="e">
-        <f>C10/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I10" s="18" t="e">
-        <f>G10/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J10" s="18" t="e">
-        <f>G10/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K10" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M10" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N10" s="19" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26834,44 +27035,44 @@
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E11" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E11" s="18" t="e">
-        <f>C11/$C$13*100</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F11" s="18" t="e">
-        <f>C11/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="18" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I11" s="18" t="e">
-        <f>G11/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J11" s="18" t="e">
-        <f>G11/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K11" s="18" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L11" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M11" s="18" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N11" s="19" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26885,11 +27086,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E12" s="18" t="e">
-        <f>C12/$C$13*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F12" s="18" t="e">
-        <f>C12/$L$13*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G12" s="17"/>
@@ -26898,11 +27099,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I12" s="18" t="e">
-        <f>G12/$G$13*100</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J12" s="18" t="e">
-        <f>G12/$L$13*100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K12" s="18" t="e">
@@ -26976,11 +27177,11 @@
         <v>0</v>
       </c>
       <c r="D17" s="21">
-        <f>C3</f>
+        <f t="shared" ref="D17:D26" si="10">C3</f>
         <v>0</v>
       </c>
       <c r="E17" s="21">
-        <f>G3</f>
+        <f t="shared" ref="E17:E26" si="11">G3</f>
         <v>0</v>
       </c>
     </row>
@@ -26989,11 +27190,11 @@
         <v>1</v>
       </c>
       <c r="D18" s="21">
-        <f>C4</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E18" s="21">
-        <f>G4</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27002,11 +27203,11 @@
         <v>2</v>
       </c>
       <c r="D19" s="21">
-        <f>C5</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E19" s="21">
-        <f>G5</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27015,11 +27216,11 @@
         <v>3</v>
       </c>
       <c r="D20" s="21">
-        <f>C6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E20" s="21">
-        <f>G6</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27028,11 +27229,11 @@
         <v>4</v>
       </c>
       <c r="D21" s="21">
-        <f>C7</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E21" s="21">
-        <f>G7</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27041,11 +27242,11 @@
         <v>5</v>
       </c>
       <c r="D22" s="21">
-        <f>C8</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E22" s="21">
-        <f>G8</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27054,11 +27255,11 @@
         <v>6</v>
       </c>
       <c r="D23" s="21">
-        <f>C9</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E23" s="21">
-        <f>G9</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27067,11 +27268,11 @@
         <v>7</v>
       </c>
       <c r="D24" s="21">
-        <f>C10</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E24" s="21">
-        <f>G10</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27080,11 +27281,11 @@
         <v>8</v>
       </c>
       <c r="D25" s="21">
-        <f>C11</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E25" s="21">
-        <f>G11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27093,11 +27294,11 @@
         <v>96</v>
       </c>
       <c r="D26" s="21">
-        <f>C12</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E26" s="21">
-        <f>G12</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27108,7 +27309,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -27452,7 +27653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -27555,7 +27756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
@@ -27657,7 +27858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -28482,7 +28683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -28886,7 +29087,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -29230,7 +29431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -29895,7 +30096,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -30490,7 +30691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30953,7 +31154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31087,7 +31288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31581,7 +31782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31924,7 +32125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -32025,7 +32226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -32124,7 +32325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Igualdad/cuadro_porcentajes/CUADRO_PORCENTAJES.xlsx
+++ b/Igualdad/cuadro_porcentajes/CUADRO_PORCENTAJES.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="9" activeTab="13"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="10" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="TOTAL PLANTILLA" sheetId="27" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="105">
   <si>
     <t>Menos de 20 años</t>
   </si>
@@ -365,12 +365,27 @@
   <si>
     <t>Hospitalizacion de familiares</t>
   </si>
+  <si>
+    <t>Horas</t>
+  </si>
+  <si>
+    <t>Modalidad</t>
+  </si>
+  <si>
+    <t>Perfil(puesto)</t>
+  </si>
+  <si>
+    <t>Horario</t>
+  </si>
+  <si>
+    <t>Carácter</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,8 +436,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,8 +470,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -497,11 +526,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -588,6 +632,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1283,7 +1331,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1568,7 +1615,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -24174,27 +24220,28 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:N7"/>
+  <dimension ref="B2:M7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>15</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>16</v>
@@ -24202,80 +24249,58 @@
       <c r="H2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>14</v>
+      <c r="I2" s="37" t="s">
+        <v>21</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="2" t="e">
-        <f>C3/L3*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E3" s="2" t="e">
+      <c r="D3" s="2"/>
+      <c r="E3" s="36" t="e">
         <f>C3/$C$4*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F3" s="2" t="e">
-        <f>C3/$L$4*100</f>
+      <c r="F3" s="36" t="e">
+        <f>D3/$C$4*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="e">
-        <f>G3/L3*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I3" s="2" t="e">
-        <f>G3/$G$4*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J3" s="2" t="e">
-        <f>G3/$L$4*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K3" s="2" t="e">
-        <f>F3+J3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L3" s="2">
+        <f>G3/I3*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I3" s="36">
         <f>C3+G3</f>
         <v>0</v>
       </c>
-      <c r="M3" s="2" t="e">
-        <f>H3-D3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N3" s="2" t="e">
-        <f>C3/G3</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C4" s="2">
         <f>SUM(C3:C3)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="e">
-        <f>SUM(E3:E3)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D4" s="2">
+        <f>SUM(D3:D3)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2" t="e">
         <f>SUM(F3:F3)</f>
         <v>#DIV/0!</v>
@@ -24285,26 +24310,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2" t="e">
+      <c r="I4" s="36">
         <f>SUM(I3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J4" s="2" t="e">
-        <f>SUM(J3:J3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K4" s="2" t="e">
-        <f>SUM(K3:K3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L4" s="2">
-        <f>SUM(L3:L3)</f>
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D6" s="12" t="s">
         <v>12</v>
       </c>
@@ -24312,10 +24327,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C7" s="5"/>
       <c r="D7" s="4">
-        <f>C3</f>
+        <f>D3</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
@@ -24325,6 +24340,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
